--- a/Handicaps & Points (Historical).xlsx
+++ b/Handicaps & Points (Historical).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/craighilts/Library/CloudStorage/Dropbox/FBC/FBC Data &amp; Apps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC59D74-8E5F-E145-BC44-DE17FE665260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26C5A42-4116-C94F-8714-5649AADC0735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8200" yWindow="600" windowWidth="33040" windowHeight="22600" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Cups!$B$3:$R$31</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="73">
   <si>
     <t>Player</t>
   </si>
@@ -255,6 +255,12 @@
   <si>
     <t>Snyder</t>
   </si>
+  <si>
+    <t>Ramsey</t>
+  </si>
+  <si>
+    <t>Connolly, B</t>
+  </si>
 </sst>
 </file>
 
@@ -351,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -411,11 +417,34 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -7490,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="24">
-        <f t="shared" ref="O3:O32" si="0">SUM(C3:N3)</f>
+        <f t="shared" ref="O3:O4" si="0">SUM(C3:N3)</f>
         <v>10</v>
       </c>
       <c r="P3" s="24">
@@ -7498,11 +7527,11 @@
         <v>12</v>
       </c>
       <c r="Q3" s="25">
-        <f t="shared" ref="Q3:Q32" si="1">O3/P3</f>
+        <f t="shared" ref="Q3:Q4" si="1">O3/P3</f>
         <v>0.83333333333333337</v>
       </c>
       <c r="R3" s="24">
-        <f t="shared" ref="R3:R32" si="2">P3-O3</f>
+        <f t="shared" ref="R3:R4" si="2">P3-O3</f>
         <v>2</v>
       </c>
       <c r="S3" s="2"/>
@@ -7512,7 +7541,7 @@
     <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C4" s="24">
         <v>1</v>
@@ -7554,17 +7583,17 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="P4" s="24">
+      <c r="P4" s="24" t="e">
         <f>VLOOKUP($B4,Points!$B$2:$C$34,2,FALSE())</f>
-        <v>12</v>
-      </c>
-      <c r="Q4" s="25">
+        <v>#N/A</v>
+      </c>
+      <c r="Q4" s="25" t="e">
         <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-      <c r="R4" s="24">
+        <v>#N/A</v>
+      </c>
+      <c r="R4" s="24" t="e">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>#N/A</v>
       </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
@@ -7612,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="O3:O32" si="3">SUM(C5:N5)</f>
         <v>8</v>
       </c>
       <c r="P5" s="24">
@@ -7620,11 +7649,11 @@
         <v>12</v>
       </c>
       <c r="Q5" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="Q3:Q32" si="4">O5/P5</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="R5" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="R3:R32" si="5">P5-O5</f>
         <v>4</v>
       </c>
       <c r="S5" s="2"/>
@@ -7673,7 +7702,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="P6" s="24">
@@ -7681,11 +7710,11 @@
         <v>11</v>
       </c>
       <c r="Q6" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.72727272727272729</v>
       </c>
       <c r="R6" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S6" s="2"/>
@@ -7734,7 +7763,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="P7" s="24">
@@ -7742,11 +7771,11 @@
         <v>11</v>
       </c>
       <c r="Q7" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.63636363636363635</v>
       </c>
       <c r="R7" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="S7" s="2"/>
@@ -7795,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="P8" s="24">
@@ -7803,11 +7832,11 @@
         <v>10</v>
       </c>
       <c r="Q8" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
       <c r="R8" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="S8" s="2"/>
@@ -7856,7 +7885,7 @@
         <v>18</v>
       </c>
       <c r="O9" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="P9" s="24">
@@ -7864,11 +7893,11 @@
         <v>8</v>
       </c>
       <c r="Q9" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.625</v>
       </c>
       <c r="R9" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S9" s="2"/>
@@ -7917,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="P10" s="24">
@@ -7925,11 +7954,11 @@
         <v>12</v>
       </c>
       <c r="Q10" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.41666666666666669</v>
       </c>
       <c r="R10" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="S10" s="2"/>
@@ -7978,7 +8007,7 @@
         <v>1</v>
       </c>
       <c r="O11" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="P11" s="24">
@@ -7986,11 +8015,11 @@
         <v>11</v>
       </c>
       <c r="Q11" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.45454545454545453</v>
       </c>
       <c r="R11" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="S11" s="2"/>
@@ -8039,7 +8068,7 @@
         <v>18</v>
       </c>
       <c r="O12" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P12" s="24">
@@ -8047,11 +8076,11 @@
         <v>10</v>
       </c>
       <c r="Q12" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="R12" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="S12" s="2"/>
@@ -8100,7 +8129,7 @@
         <v>18</v>
       </c>
       <c r="O13" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P13" s="24">
@@ -8108,11 +8137,11 @@
         <v>10</v>
       </c>
       <c r="Q13" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="R13" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="S13" s="2"/>
@@ -8161,7 +8190,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P14" s="24">
@@ -8169,11 +8198,11 @@
         <v>6</v>
       </c>
       <c r="Q14" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="R14" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S14" s="2"/>
@@ -8222,7 +8251,7 @@
         <v>18</v>
       </c>
       <c r="O15" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P15" s="24">
@@ -8230,11 +8259,11 @@
         <v>7</v>
       </c>
       <c r="Q15" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="R15" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S15" s="2"/>
@@ -8283,7 +8312,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P16" s="24">
@@ -8291,11 +8320,11 @@
         <v>12</v>
       </c>
       <c r="Q16" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="R16" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="S16" s="2"/>
@@ -8344,7 +8373,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P17" s="24">
@@ -8352,11 +8381,11 @@
         <v>4</v>
       </c>
       <c r="Q17" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="R17" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S17" s="2"/>
@@ -8405,7 +8434,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="P18" s="24">
@@ -8413,11 +8442,11 @@
         <v>11</v>
       </c>
       <c r="Q18" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.36363636363636365</v>
       </c>
       <c r="R18" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="S18" s="2"/>
@@ -8466,18 +8495,18 @@
         <v>18</v>
       </c>
       <c r="O19" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P19" s="24">
         <v>6</v>
       </c>
       <c r="Q19" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="R19" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S19" s="2"/>
@@ -8526,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P20" s="24">
@@ -8534,11 +8563,11 @@
         <v>12</v>
       </c>
       <c r="Q20" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
       <c r="R20" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="S20" s="2"/>
@@ -8587,7 +8616,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P21" s="24">
@@ -8595,11 +8624,11 @@
         <v>11</v>
       </c>
       <c r="Q21" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.27272727272727271</v>
       </c>
       <c r="R21" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="S21" s="2"/>
@@ -8648,7 +8677,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P22" s="24">
@@ -8656,11 +8685,11 @@
         <v>7</v>
       </c>
       <c r="Q22" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="R22" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="S22" s="2"/>
@@ -8709,18 +8738,18 @@
         <v>18</v>
       </c>
       <c r="O23" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P23" s="24">
         <v>4</v>
       </c>
       <c r="Q23" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="R23" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S23" s="2"/>
@@ -8769,7 +8798,7 @@
         <v>18</v>
       </c>
       <c r="O24" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P24" s="24">
@@ -8777,11 +8806,11 @@
         <v>8</v>
       </c>
       <c r="Q24" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
       <c r="R24" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="S24" s="2"/>
@@ -8830,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P25" s="24">
@@ -8838,11 +8867,11 @@
         <v>5</v>
       </c>
       <c r="Q25" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="R25" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="S25" s="2"/>
@@ -8891,7 +8920,7 @@
         <v>18</v>
       </c>
       <c r="O26" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P26" s="24">
@@ -8899,11 +8928,11 @@
         <v>6</v>
       </c>
       <c r="Q26" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="R26" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="S26" s="2"/>
@@ -8952,18 +8981,19 @@
         <v>0</v>
       </c>
       <c r="O27" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P27" s="24">
-        <v>2</v>
+        <f>VLOOKUP($B27,Points!$B$2:$C$34,2,FALSE())</f>
+        <v>3</v>
       </c>
       <c r="Q27" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="R27" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S27" s="2"/>
@@ -9012,18 +9042,18 @@
         <v>18</v>
       </c>
       <c r="O28" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P28" s="24">
         <v>1</v>
       </c>
       <c r="Q28" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="R28" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S28" s="2"/>
@@ -9072,18 +9102,18 @@
         <v>18</v>
       </c>
       <c r="O29" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P29" s="24">
         <v>3</v>
       </c>
       <c r="Q29" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="R29" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="S29" s="2"/>
@@ -9132,18 +9162,19 @@
         <v>0</v>
       </c>
       <c r="O30" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P30" s="24">
-        <v>1</v>
+        <f>VLOOKUP($B30,Points!$B$2:$C$34,2,FALSE())</f>
+        <v>2</v>
       </c>
       <c r="Q30" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="R30" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S30" s="2"/>
@@ -9192,18 +9223,18 @@
         <v>1</v>
       </c>
       <c r="O31" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P31" s="24">
         <v>1</v>
       </c>
       <c r="Q31" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="R31" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S31" s="2"/>
@@ -9252,18 +9283,19 @@
         <v>0</v>
       </c>
       <c r="O32" s="24">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P32" s="24">
-        <v>1</v>
+        <f>VLOOKUP($B32,Points!$B$2:$C$34,2,FALSE())</f>
+        <v>2</v>
       </c>
       <c r="Q32" s="25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R32" s="24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="S32" s="2"/>
@@ -9272,20 +9304,48 @@
     </row>
     <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="27">
+        <v>0</v>
+      </c>
+      <c r="K33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="N33" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33" s="27" t="s">
+        <v>18</v>
+      </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
@@ -9299,60 +9359,60 @@
         <v>48</v>
       </c>
       <c r="C34" s="24">
-        <f t="shared" ref="C34:K34" si="3">SUM(C3:C30)</f>
+        <f t="shared" ref="C34:K34" si="6">SUM(C3:C33)</f>
         <v>6</v>
       </c>
       <c r="D34" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="E34" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="F34" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="G34" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="H34" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="I34" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="J34" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="K34" s="24">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="L34" s="24">
-        <f>SUM(L3:L31)</f>
+        <f>SUM(L3:L33)</f>
         <v>10</v>
       </c>
       <c r="M34" s="24">
-        <f>SUM(M3:M31)</f>
+        <f>SUM(M3:M33)</f>
         <v>10</v>
       </c>
       <c r="N34" s="24">
-        <f>SUM(N3:N31)</f>
+        <f>SUM(N3:N33)</f>
         <v>11</v>
       </c>
       <c r="O34" s="24">
-        <f>SUM(O3:O30)</f>
-        <v>115</v>
-      </c>
-      <c r="P34" s="24">
-        <f>SUM(P3:P31)</f>
-        <v>226</v>
+        <f>SUM(O3:O33)</f>
+        <v>116</v>
+      </c>
+      <c r="P34" s="24" t="e">
+        <f>SUM(P3:P33)</f>
+        <v>#N/A</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
@@ -9490,10 +9550,18 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="C3:N32">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Handicaps & Points (Historical).xlsx
+++ b/Handicaps & Points (Historical).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/craighilts/Library/CloudStorage/Dropbox/FBC/FBC Data &amp; Apps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F26C5A42-4116-C94F-8714-5649AADC0735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B91CF2-3D53-0D48-964D-5C05BB048B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8200" yWindow="600" windowWidth="33040" windowHeight="22600" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Cups!$B$3:$R$31</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -256,10 +256,10 @@
     <t>Snyder</t>
   </si>
   <si>
-    <t>Ramsey</t>
+    <t>Connolly, B</t>
   </si>
   <si>
-    <t>Connolly, B</t>
+    <t>Ramsay</t>
   </si>
 </sst>
 </file>
@@ -414,11 +414,11 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -741,14 +741,14 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
@@ -7541,7 +7541,7 @@
     <row r="4" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="24">
         <v>1</v>
@@ -7583,17 +7583,17 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="P4" s="24" t="e">
+      <c r="P4" s="24">
         <f>VLOOKUP($B4,Points!$B$2:$C$34,2,FALSE())</f>
-        <v>#N/A</v>
-      </c>
-      <c r="Q4" s="25" t="e">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="25">
         <f t="shared" si="1"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R4" s="24" t="e">
+        <v>0.75</v>
+      </c>
+      <c r="R4" s="24">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
+        <v>3</v>
       </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
@@ -7641,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="24">
-        <f t="shared" ref="O3:O32" si="3">SUM(C5:N5)</f>
+        <f t="shared" ref="O5:O32" si="3">SUM(C5:N5)</f>
         <v>8</v>
       </c>
       <c r="P5" s="24">
@@ -7649,11 +7649,11 @@
         <v>12</v>
       </c>
       <c r="Q5" s="25">
-        <f t="shared" ref="Q3:Q32" si="4">O5/P5</f>
+        <f t="shared" ref="Q5:Q32" si="4">O5/P5</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="R5" s="24">
-        <f t="shared" ref="R3:R32" si="5">P5-O5</f>
+        <f t="shared" ref="R5:R32" si="5">P5-O5</f>
         <v>4</v>
       </c>
       <c r="S5" s="2"/>
@@ -8990,11 +8990,11 @@
       </c>
       <c r="Q27" s="25">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="R27" s="24">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
@@ -9171,11 +9171,11 @@
       </c>
       <c r="Q30" s="25">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="R30" s="24">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="R32" s="24">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
@@ -9305,45 +9305,45 @@
     <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="H33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="I33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J33" s="27">
-        <v>0</v>
-      </c>
-      <c r="K33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="L33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="M33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="N33" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="O33" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="26">
+        <v>0</v>
+      </c>
+      <c r="K33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N33" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33" s="26" t="s">
         <v>18</v>
       </c>
       <c r="P33" s="2"/>
@@ -9410,9 +9410,9 @@
         <f>SUM(O3:O33)</f>
         <v>116</v>
       </c>
-      <c r="P34" s="24" t="e">
+      <c r="P34" s="24">
         <f>SUM(P3:P33)</f>
-        <v>#N/A</v>
+        <v>230</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
